--- a/TEST_PLAN.xlsx
+++ b/TEST_PLAN.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr"/>
@@ -720,7 +720,7 @@
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="K3" s="6" t="inlineStr"/>
@@ -777,7 +777,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr"/>
@@ -891,7 +891,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr"/>
@@ -947,7 +947,7 @@
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr"/>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr"/>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr"/>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr"/>
@@ -3213,7 +3213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3240,212 +3240,212 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Future scope</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
+          <t>Future scope</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
           <t>Total written up</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B6" s="16" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Everything below counts the working set only.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>By suite</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>Cases</t>
         </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Smoke</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sanity</t>
+          <t>Smoke</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Sanity</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Regression</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B13" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B14" s="16" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>By priority</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Cases</t>
         </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B20" s="16" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>By scope</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>Cases</t>
         </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>End-to-End</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B25" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n">
+      <c r="B26" s="16" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>By feature area</t>
         </is>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>Cases</t>
         </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Interface</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Catalogue</t>
+          <t>Interface</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -3455,7 +3455,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Product detail</t>
+          <t>Catalogue</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -3465,7 +3465,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cart</t>
+          <t>Product detail</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -3475,90 +3475,100 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Cart</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Guest flow</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Checkout</t>
+          <t>Guest flow</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Checkout</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Orders</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Orders</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Test API</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Test API</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Framework</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B40" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="16" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n">
+      <c r="B41" s="16" t="n">
         <v>18</v>
       </c>
     </row>
